--- a/evidence/s03a/normal/s02a_shipments.xlsx
+++ b/evidence/s03a/normal/s02a_shipments.xlsx
@@ -78,7 +78,7 @@
     <t>snapshot_id</t>
   </si>
   <si>
-    <t>9f055e1bcfc169583e55d1655b19bb71</t>
+    <t>54a9ea142f1f1c5d85c7608249a59715</t>
   </si>
   <si>
     <t>integration_id</t>
@@ -120,13 +120,13 @@
     <t>source_snapshot_ref</t>
   </si>
   <si>
-    <t>19fa028814553c13a8aae74aa4943d6f</t>
+    <t>b6d5db402f6e613aa850ede49bebb4ee</t>
   </si>
   <si>
     <t>expires_at</t>
   </si>
   <si>
-    <t>2026-10-27T00:00:27+08:00</t>
+    <t>2026-10-27T00:27:02+08:00</t>
   </si>
   <si>
     <t>precision</t>

--- a/evidence/s03a/normal/s02a_shipments.xlsx
+++ b/evidence/s03a/normal/s02a_shipments.xlsx
@@ -78,7 +78,7 @@
     <t>snapshot_id</t>
   </si>
   <si>
-    <t>54a9ea142f1f1c5d85c7608249a59715</t>
+    <t>e7b64090254a95e6c4fd998642445051</t>
   </si>
   <si>
     <t>integration_id</t>
@@ -120,13 +120,13 @@
     <t>source_snapshot_ref</t>
   </si>
   <si>
-    <t>b6d5db402f6e613aa850ede49bebb4ee</t>
+    <t>e3e0a4befbd02d5cfea931b244a4a0a8</t>
   </si>
   <si>
     <t>expires_at</t>
   </si>
   <si>
-    <t>2026-10-27T00:27:02+08:00</t>
+    <t>2026-10-27T00:32:44+08:00</t>
   </si>
   <si>
     <t>precision</t>

--- a/evidence/s03a/normal/s02a_shipments.xlsx
+++ b/evidence/s03a/normal/s02a_shipments.xlsx
@@ -78,7 +78,7 @@
     <t>snapshot_id</t>
   </si>
   <si>
-    <t>e7b64090254a95e6c4fd998642445051</t>
+    <t>be4a3111a828e9b9b4f7379c2b5d7be1</t>
   </si>
   <si>
     <t>integration_id</t>
@@ -120,13 +120,13 @@
     <t>source_snapshot_ref</t>
   </si>
   <si>
-    <t>e3e0a4befbd02d5cfea931b244a4a0a8</t>
+    <t>885324db31276c1d9f169b03910e3e1c</t>
   </si>
   <si>
     <t>expires_at</t>
   </si>
   <si>
-    <t>2026-10-27T00:32:44+08:00</t>
+    <t>2026-10-27T00:40:39+08:00</t>
   </si>
   <si>
     <t>precision</t>
